--- a/CordicAmmar/opravljenoDelo/CordicAmmar.xlsx
+++ b/CordicAmmar/opravljenoDelo/CordicAmmar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ammar\Desktop\Škola\Računalništvo v oblaku\Izpit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ammar\Personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B02DA1-0C9E-462A-8C9A-5A1F4A5AFEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD5DE00-339F-4B30-907C-CAFA6E778EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30600" yWindow="1140" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -424,7 +424,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,6 +449,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -643,7 +649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -660,9 +666,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -672,39 +675,51 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Navadno" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -983,17 +998,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:N31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.26953125" customWidth="1"/>
-    <col min="6" max="6" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="17" width="12.26953125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="17" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>1</v>
       </c>
@@ -1031,7 +1046,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -1069,7 +1084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1104,7 +1119,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>14</v>
       </c>
@@ -1127,7 +1142,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>4</v>
       </c>
@@ -1147,7 +1162,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>5</v>
       </c>
@@ -1167,7 +1182,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>6</v>
       </c>
@@ -1181,7 +1196,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>3</v>
       </c>
@@ -1195,7 +1210,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
@@ -1206,27 +1221,27 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>1</v>
       </c>
@@ -1264,7 +1279,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>2</v>
       </c>
@@ -1293,7 +1308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>2</v>
       </c>
@@ -1307,7 +1322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>3</v>
       </c>
@@ -1336,7 +1351,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>4</v>
       </c>
@@ -1350,7 +1365,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>4</v>
       </c>
@@ -1370,7 +1385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>5</v>
       </c>
@@ -1378,7 +1393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>6</v>
       </c>
@@ -1404,7 +1419,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>7</v>
       </c>
@@ -1415,7 +1430,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>7</v>
       </c>
@@ -1435,7 +1450,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>8</v>
       </c>
@@ -1446,7 +1461,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>8</v>
       </c>
@@ -1466,58 +1481,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E560E397-08D2-4940-85D9-6188CD094F12}">
   <dimension ref="B1:P26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="2" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" style="3" customWidth="1"/>
-    <col min="4" max="16" width="17.54296875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="3" customWidth="1"/>
+    <col min="4" max="16" width="17.5703125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="12">
+    <row r="1" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="B2" s="11">
         <v>1</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="22" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="203" x14ac:dyDescent="0.35">
-      <c r="B3" s="14"/>
-      <c r="C3" s="15"/>
+    <row r="3" spans="2:16" ht="225" x14ac:dyDescent="0.25">
+      <c r="B3" s="13"/>
+      <c r="C3" s="14"/>
       <c r="D3" s="5" t="s">
         <v>57</v>
       </c>
@@ -1551,21 +1566,21 @@
       <c r="N3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P3" s="8" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B4" s="16">
+    <row r="4" spans="2:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="B4" s="15">
         <v>1</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="22" t="s">
         <v>47</v>
       </c>
       <c r="F4" s="4"/>
@@ -1577,49 +1592,49 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-      <c r="P4" s="10" t="s">
+      <c r="P4" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B5" s="16">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" s="15">
         <v>2</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="22" t="s">
         <v>18</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="7"/>
-      <c r="P5" s="11" t="s">
+      <c r="P5" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="145" x14ac:dyDescent="0.35">
-      <c r="B6" s="16"/>
-      <c r="C6" s="17"/>
+    <row r="6" spans="2:16" ht="180" x14ac:dyDescent="0.25">
+      <c r="B6" s="15"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="5" t="s">
         <v>58</v>
       </c>
@@ -1644,23 +1659,23 @@
       <c r="M6" s="4"/>
       <c r="N6" s="7"/>
     </row>
-    <row r="7" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B7" s="16">
+    <row r="7" spans="2:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="B7" s="15">
         <v>2</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="22" t="s">
         <v>59</v>
       </c>
       <c r="H7" s="4"/>
@@ -1671,9 +1686,9 @@
       <c r="M7" s="4"/>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" spans="2:16" ht="246.5" x14ac:dyDescent="0.35">
-      <c r="B8" s="16"/>
-      <c r="C8" s="17"/>
+    <row r="8" spans="2:16" ht="285" x14ac:dyDescent="0.25">
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="6" t="s">
         <v>65</v>
       </c>
@@ -1692,29 +1707,29 @@
       <c r="M8" s="4"/>
       <c r="N8" s="7"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B9" s="16">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B9" s="15">
         <v>3</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="C9" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="22" t="s">
         <v>26</v>
       </c>
       <c r="J9" s="4"/>
@@ -1723,9 +1738,9 @@
       <c r="M9" s="4"/>
       <c r="N9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="116" x14ac:dyDescent="0.35">
-      <c r="B10" s="16"/>
-      <c r="C10" s="17"/>
+    <row r="10" spans="2:16" ht="120" x14ac:dyDescent="0.25">
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="6" t="s">
         <v>69</v>
       </c>
@@ -1750,17 +1765,17 @@
       <c r="M10" s="4"/>
       <c r="N10" s="7"/>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B11" s="16">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B11" s="15">
         <v>4</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="C11" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="22" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="4"/>
@@ -1773,9 +1788,9 @@
       <c r="M11" s="4"/>
       <c r="N11" s="7"/>
     </row>
-    <row r="12" spans="2:16" ht="174" x14ac:dyDescent="0.35">
-      <c r="B12" s="16"/>
-      <c r="C12" s="17"/>
+    <row r="12" spans="2:16" ht="195" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
       <c r="D12" s="6" t="s">
         <v>76</v>
       </c>
@@ -1792,23 +1807,23 @@
       <c r="M12" s="4"/>
       <c r="N12" s="7"/>
     </row>
-    <row r="13" spans="2:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="B13" s="16">
+    <row r="13" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B13" s="15">
         <v>4</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="22" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="4"/>
@@ -1819,9 +1834,9 @@
       <c r="M13" s="4"/>
       <c r="N13" s="7"/>
     </row>
-    <row r="14" spans="2:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="B14" s="16"/>
-      <c r="C14" s="17"/>
+    <row r="14" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B14" s="15"/>
+      <c r="C14" s="16"/>
       <c r="D14" s="6" t="s">
         <v>78</v>
       </c>
@@ -1838,23 +1853,23 @@
       <c r="M14" s="4"/>
       <c r="N14" s="7"/>
     </row>
-    <row r="15" spans="2:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="B15" s="16">
+    <row r="15" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="15">
         <v>5</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="C15" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="22" t="s">
         <v>32</v>
       </c>
       <c r="H15" s="4"/>
@@ -1865,9 +1880,9 @@
       <c r="M15" s="4"/>
       <c r="N15" s="7"/>
     </row>
-    <row r="16" spans="2:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B16" s="16"/>
-      <c r="C16" s="17"/>
+    <row r="16" spans="2:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
       <c r="D16" s="6" t="s">
         <v>80</v>
       </c>
@@ -1888,17 +1903,17 @@
       <c r="M16" s="4"/>
       <c r="N16" s="7"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B17" s="16">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B17" s="15">
         <v>5</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="22" t="s">
         <v>78</v>
       </c>
       <c r="F17" s="4"/>
@@ -1911,9 +1926,9 @@
       <c r="M17" s="4"/>
       <c r="N17" s="7"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B18" s="16"/>
-      <c r="C18" s="17"/>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
       <c r="D18" s="6"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -1926,26 +1941,26 @@
       <c r="M18" s="4"/>
       <c r="N18" s="7"/>
     </row>
-    <row r="19" spans="2:14" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B19" s="16">
+    <row r="19" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="B19" s="15">
         <v>6</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="C19" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="22" t="s">
         <v>93</v>
       </c>
       <c r="I19" s="4"/>
@@ -1955,9 +1970,9 @@
       <c r="M19" s="4"/>
       <c r="N19" s="7"/>
     </row>
-    <row r="20" spans="2:14" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="B20" s="16"/>
-      <c r="C20" s="17"/>
+    <row r="20" spans="2:14" ht="120" x14ac:dyDescent="0.25">
+      <c r="B20" s="15"/>
+      <c r="C20" s="16"/>
       <c r="D20" s="6" t="s">
         <v>91</v>
       </c>
@@ -1976,17 +1991,17 @@
       <c r="M20" s="4"/>
       <c r="N20" s="7"/>
     </row>
-    <row r="21" spans="2:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="B21" s="16">
+    <row r="21" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B21" s="15">
         <v>7</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="C21" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="22" t="s">
         <v>95</v>
       </c>
       <c r="F21" s="4"/>
@@ -1999,9 +2014,9 @@
       <c r="M21" s="4"/>
       <c r="N21" s="7"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B22" s="16"/>
-      <c r="C22" s="17"/>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B22" s="15"/>
+      <c r="C22" s="16"/>
       <c r="D22" s="6" t="s">
         <v>94</v>
       </c>
@@ -2016,26 +2031,26 @@
       <c r="M22" s="4"/>
       <c r="N22" s="7"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B23" s="16">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B23" s="15">
         <v>7</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="22" t="s">
         <v>96</v>
       </c>
       <c r="I23" s="4"/>
@@ -2045,14 +2060,14 @@
       <c r="M23" s="4"/>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B24" s="16">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B24" s="15">
         <v>8</v>
       </c>
-      <c r="C24" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6" t="s">
+      <c r="C24" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="23" t="s">
         <v>40</v>
       </c>
       <c r="E24" s="4"/>
@@ -2066,14 +2081,14 @@
       <c r="M24" s="4"/>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B25" s="18">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B25" s="17">
         <v>8</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="23" t="s">
         <v>40</v>
       </c>
       <c r="E25" s="4"/>
@@ -2087,14 +2102,14 @@
       <c r="M25" s="4"/>
       <c r="N25" s="7"/>
     </row>
-    <row r="26" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="20">
+    <row r="26" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="19">
         <v>9</v>
       </c>
-      <c r="C26" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="C26" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="24" t="s">
         <v>40</v>
       </c>
     </row>

--- a/CordicAmmar/opravljenoDelo/CordicAmmar.xlsx
+++ b/CordicAmmar/opravljenoDelo/CordicAmmar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ammar\Personal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD5DE00-339F-4B30-907C-CAFA6E778EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8613AC-8152-4708-A95F-89B243A7C243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30600" yWindow="1140" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -715,6 +715,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1526,7 +1529,7 @@
       <c r="M2" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="25" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1726,7 +1729,7 @@
       <c r="G9" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="25" t="s">
         <v>72</v>
       </c>
       <c r="I9" s="22" t="s">
